--- a/tests/single_cif_file_test/560709/output/560709_pairs.xlsx
+++ b/tests/single_cif_file_test/560709/output/560709_pairs.xlsx
@@ -7,11 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Ga" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ga" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Co" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Ga" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Co" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ga" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
